--- a/output/sliding_window_results_window_1.xlsx
+++ b/output/sliding_window_results_window_1.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>28.98</v>
+        <v>32.28</v>
       </c>
       <c r="C2" t="n">
-        <v>25.91097972534909</v>
+        <v>33.01847653924242</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.06902027465091</v>
+        <v>0.73847653924242</v>
       </c>
       <c r="E2" t="n">
-        <v>9.418885446218347</v>
+        <v>0.5453475990114615</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>29.54</v>
+        <v>33.1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.47271017517513</v>
+        <v>31.46029783843635</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.067289824824869</v>
+        <v>-1.639702161563655</v>
       </c>
       <c r="E3" t="n">
-        <v>16.54284651912391</v>
+        <v>2.688623178636521</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>29.81</v>
+        <v>34.4</v>
       </c>
       <c r="C4" t="n">
-        <v>27.78396322881116</v>
+        <v>36.69773732046712</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.026036771188842</v>
+        <v>2.297737320467121</v>
       </c>
       <c r="E4" t="n">
-        <v>4.104824998209309</v>
+        <v>5.279596793867425</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>30.21</v>
+        <v>36.3</v>
       </c>
       <c r="C5" t="n">
-        <v>27.59467326021365</v>
+        <v>36.48708454927768</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.615326739786354</v>
+        <v>0.1870845492776851</v>
       </c>
       <c r="E5" t="n">
-        <v>6.839933955841522</v>
+        <v>0.0350006285784346</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>30.48</v>
+        <v>38.5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.73326315493976</v>
+        <v>41.67109861835181</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.746736845060241</v>
+        <v>3.171098618351806</v>
       </c>
       <c r="E6" t="n">
-        <v>3.051089605891003</v>
+        <v>10.05586644731273</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>30.95</v>
+        <v>40.1</v>
       </c>
       <c r="C7" t="n">
-        <v>29.78957402937299</v>
+        <v>46.08792561060294</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.160425970627013</v>
+        <v>5.987925610602936</v>
       </c>
       <c r="E7" t="n">
-        <v>1.346588433305646</v>
+        <v>35.85525311811454</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>31.38</v>
+        <v>41.5</v>
       </c>
       <c r="C8" t="n">
-        <v>31.01838586696742</v>
+        <v>48.22491584872444</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3616141330325746</v>
+        <v>6.724915848724436</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1307647812089006</v>
+        <v>45.2244931724251</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>32.28</v>
+        <v>43.7</v>
       </c>
       <c r="C9" t="n">
-        <v>31.88976476734676</v>
+        <v>48.6874837421374</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.390235232653243</v>
+        <v>4.9874837421374</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1522835368039307</v>
+        <v>24.87499407808488</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>33.1</v>
+        <v>48.1</v>
       </c>
       <c r="C10" t="n">
-        <v>30.6693980195681</v>
+        <v>54.40016884586725</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.430601980431906</v>
+        <v>6.300168845867248</v>
       </c>
       <c r="E10" t="n">
-        <v>5.907825987279502</v>
+        <v>39.69212748643625</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C11" t="n">
-        <v>32.11464628277592</v>
+        <v>55.66198596987874</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.285353717224076</v>
+        <v>2.661985969878735</v>
       </c>
       <c r="E11" t="n">
-        <v>5.222841612829903</v>
+        <v>7.08616930383123</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C12" t="n">
-        <v>34.12246503003058</v>
+        <v>62.91001769901384</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.177534969969422</v>
+        <v>6.810017699013841</v>
       </c>
       <c r="E12" t="n">
-        <v>4.741658545439731</v>
+        <v>46.37634106088176</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C13" t="n">
-        <v>36.80791184140291</v>
+        <v>65.47533969655228</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.692088158597087</v>
+        <v>5.475339696552282</v>
       </c>
       <c r="E13" t="n">
-        <v>2.863162336464482</v>
+        <v>29.97934479264124</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C14" t="n">
-        <v>39.32793523877074</v>
+        <v>70.15103769568275</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7720647612292595</v>
+        <v>6.251037695682747</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5960839955319934</v>
+        <v>39.07547227284667</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>40.87693323135697</v>
+        <v>76.71164434130182</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.623066768643028</v>
+        <v>6.111644341301826</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3882121981872646</v>
+        <v>37.35219655456663</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>44.73124351347364</v>
+        <v>87.19830692933584</v>
       </c>
       <c r="D16" t="n">
-        <v>1.03124351347364</v>
+        <v>6.298306929335837</v>
       </c>
       <c r="E16" t="n">
-        <v>1.063463184081458</v>
+        <v>39.66867017611982</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>47.49666486264427</v>
+        <v>89.91446957359877</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6033351373557352</v>
+        <v>0.814469573598771</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3640132879680638</v>
+        <v>0.6633606863181639</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C18" t="n">
-        <v>55.31849097247884</v>
+        <v>87.72619929330028</v>
       </c>
       <c r="D18" t="n">
-        <v>2.318490972478841</v>
+        <v>-7.273800706699717</v>
       </c>
       <c r="E18" t="n">
-        <v>5.375400389465883</v>
+        <v>52.9081767207853</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C19" t="n">
-        <v>53.28054649156012</v>
+        <v>97.1279690936323</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.819453508439885</v>
+        <v>-1.672030906367695</v>
       </c>
       <c r="E19" t="n">
-        <v>7.949318086253977</v>
+        <v>2.795687351848776</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C20" t="n">
-        <v>57.42472159824418</v>
+        <v>106.6032232075476</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.575278401755824</v>
+        <v>3.303223207547589</v>
       </c>
       <c r="E20" t="n">
-        <v>6.632058846550032</v>
+        <v>10.91128355888098</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C21" t="n">
-        <v>53.95296500633222</v>
+        <v>116.0635172878329</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.947034993667778</v>
+        <v>9.063517287832909</v>
       </c>
       <c r="E21" t="n">
-        <v>98.94350516525132</v>
+        <v>82.147345626846</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-38.01276370318557</v>
+        <v>66.59889970078453</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>181.6347609119062</v>
+        <v>513.215350608034</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>9.08173804559531</v>
+        <v>25.6607675304017</v>
       </c>
     </row>
   </sheetData>
